--- a/Project/Beyes/metrics_summary.xlsx
+++ b/Project/Beyes/metrics_summary.xlsx
@@ -452,16 +452,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110.7608695652174</v>
+        <v>149.4565217391304</v>
       </c>
       <c r="B2" t="n">
-        <v>94.34782608695649</v>
+        <v>150.7608695652174</v>
       </c>
       <c r="C2" t="n">
-        <v>76.19565217391306</v>
+        <v>130.8695652173913</v>
       </c>
       <c r="D2" t="n">
-        <v>7776.630434782611</v>
+        <v>15611.95652173913</v>
       </c>
     </row>
   </sheetData>
